--- a/my-app/client/public/bank.xlsx
+++ b/my-app/client/public/bank.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\pfe\my-app\client\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3156046-44C4-436E-9E40-CCB5EEA66B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
   <si>
     <t>BL</t>
   </si>
@@ -147,22 +152,74 @@
   </si>
   <si>
     <t>2026-04-08T23:00:00.000Z</t>
+  </si>
+  <si>
+    <t>BL-100</t>
+  </si>
+  <si>
+    <t>tr400</t>
+  </si>
+  <si>
+    <t>yanis</t>
+  </si>
+  <si>
+    <t>1000.00</t>
+  </si>
+  <si>
+    <t>2026-01-10T00:00:00.000Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFFF7B72"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFD2A8FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF8B949E"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFA5D6FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFFFA657"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -170,28 +227,58 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -481,14 +568,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -534,7 +618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -557,7 +641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -571,7 +655,7 @@
         <v>22</v>
       </c>
       <c r="E4">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -580,7 +664,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -603,7 +687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -617,7 +701,7 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="F6" t="s">
         <v>31</v>
@@ -626,7 +710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -640,7 +724,7 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -649,7 +733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -663,7 +747,7 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="F8" t="s">
         <v>35</v>
@@ -672,7 +756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -686,7 +770,7 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>300000.0</v>
+        <v>300000</v>
       </c>
       <c r="F9" t="s">
         <v>37</v>
@@ -695,7 +779,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -718,7 +802,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -741,18 +825,81 @@
         <v>12</v>
       </c>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>